--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5985</v>
+        <v>5680</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.88%1140</t>
+          <t>-4.82%1085</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2985</v>
+        <v>2865</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.43%562</t>
+          <t>-1.42%554</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6325</v>
+        <v>6255</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.52%5650</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5650</v>
+        <v>5465</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2105</v>
+        <v>2035</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.56%5600</t>
+          <t>-3.66%5395</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5600</v>
+        <v>5395</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.13%1745</t>
+          <t>+0.29%1750</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.27%2250</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:02</t>
+          <t>2026-08-21 14:41:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%115.5</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,17 +1424,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5%1575</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.51%15750</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0%1850</t>
+          <t>-4.59%1765</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0%235</t>
+          <t>-1.28%232</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>232</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.13%964</t>
+          <t>-2.07%944</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>944</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.44%1025</t>
+          <t>-5.85%965</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>965</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7.75%570</t>
+          <t>+1.23%577</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7.75%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>577</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.76%2760</t>
+          <t>-3.99%2650</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.97%208.5</t>
+          <t>-2.64%203</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>203</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-3.96%1090</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+6.33%5630</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.31%463</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>441</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:03</t>
+          <t>2026-08-21 14:41:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.07%1265</t>
+          <t>-5.53%1195</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.15%180</t>
+          <t>+3.89%187</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+3.89%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2367,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.03%196</t>
+          <t>-1.79%192.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>196</v>
+        <v>192.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2428,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.12%82.6</t>
+          <t>-0.73%82</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>82.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2489,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.07%188.5</t>
+          <t>-2.92%183</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>188.5</v>
+        <v>183</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.58%567</t>
+          <t>-0.18%566</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.11%19.35</t>
+          <t>+0.52%19.45</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.11%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.35</v>
+        <v>19.45</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.16%94.7</t>
+          <t>+7.71%102</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.16%</t>
+          <t>+7.71%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>94.7</v>
+        <v>102</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.73%413.5</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>413.5</v>
+        <v>436</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.31%3750</t>
+          <t>-1.33%3700</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.31%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3750</v>
+        <v>3700</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.67%82</t>
+          <t>+0.61%82.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.41%1420</t>
+          <t>+1.06%1435</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1420</v>
+        <v>1435</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.21%327</t>
+          <t>-1.68%321.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>327</v>
+        <v>321.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+7.48%517</t>
+          <t>+2.13%528</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+7.48%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:04</t>
+          <t>2026-08-21 14:41:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.16%6380</t>
+          <t>+0.31%6400</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6380</v>
+        <v>6400</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.02%993</t>
+          <t>-5.24%941</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>993</v>
+        <v>941</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.82%217.5</t>
+          <t>-1.84%213.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.82%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>217.5</v>
+        <v>213.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.69%87.9</t>
+          <t>-1.37%86.7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>87.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.61%246.5</t>
+          <t>-0.41%245.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>246.5</v>
+        <v>245.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-1.3%151.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>153.5</v>
+        <v>151.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:05</t>
+          <t>2026-08-21 14:41:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.47%138.5</t>
+          <t>-3.97%133</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>138.5</v>
+        <v>133</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:00</t>
+          <t>2026-08-21 14:48:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:02</t>
+          <t>2026-08-21 14:48:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:04</t>
+          <t>2026-08-21 14:48:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:05</t>
+          <t>2026-08-21 14:48:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:19</t>
+          <t>2026-08-21 14:54:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:22</t>
+          <t>2026-08-21 14:54:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:23</t>
+          <t>2026-08-21 14:54:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:48:24</t>
+          <t>2026-08-21 14:54:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,38 +504,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.1%5680</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5680</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.08%4,843,000</t>
+          <t>10.16%11,884,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>10.16%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4843000</v>
+        <v>11884000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.47%2410</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2410</v>
+        <v>5680</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.82%11,884,000</t>
+          <t>9.76%4,843,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.82%</t>
+          <t>9.76%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11884000</v>
+        <v>4843000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.05%20,300,000</t>
+          <t>7.82%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.05%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.62%5,148,000</t>
+          <t>6.92%5,148,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.12%5,899,000</t>
+          <t>6.00%5,899,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.96%25,387,000</t>
+          <t>4.99%25,387,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.90%2,226,000</t>
+          <t>4.94%2,226,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.88%2,486,000</t>
+          <t>4.82%2,486,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.81%6,564,000</t>
+          <t>4.74%6,564,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.66%2,395,000</t>
+          <t>4.59%2,395,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.27%7,040,000</t>
+          <t>4.37%7,040,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.02%1135</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1135</v>
+        <v>587</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.00%9,624,000</t>
+          <t>4.06%19,479,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9624000</v>
+        <v>19479000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.51%587</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>587</v>
+        <v>1135</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.00%19,479,000</t>
+          <t>3.88%9,624,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>19479000</v>
+        <v>9624000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.66%4,671,848</t>
+          <t>3.77%4,671,848</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:29</t>
+          <t>2026-08-21 17:26:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.52%87,518,000</t>
+          <t>3.62%87,518,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.01%5,498,000</t>
+          <t>2.92%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.25%410,900</t>
+          <t>2.24%410,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.46%2,264,000</t>
+          <t>1.42%2,264,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.92%11,275,450</t>
+          <t>0.93%11,275,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1754,16 +1754,16 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.71%2,000,000</t>
+          <t>0.67%1,957,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2000000</v>
+        <v>1957000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.48%2,424,000</t>
+          <t>0.50%2,424,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.46%477,000</t>
+          <t>0.45%477,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,27 +2175,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.87%2100</t>
+          <t>+3.89%187</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+3.89%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.22%294,000</t>
+          <t>0.22%3,249,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>294000</v>
+        <v>3249000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:30</t>
+          <t>2026-08-21 17:26:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.21%483,000</t>
+          <t>0.20%483,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.89%187</t>
+          <t>-1.79%192.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.89%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>187</v>
+        <v>192.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.20%3,249,000</t>
+          <t>0.15%2,223,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3249000</v>
+        <v>2223000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,34 +2362,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.79%192.5</t>
+          <t>-0.73%82</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>192.5</v>
+        <v>82</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.15%2,223,000</t>
+          <t>0.12%3,988,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2223000</v>
+        <v>3988000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,25 +2423,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.73%82</t>
+          <t>-2.92%183</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.11%3,988,000</t>
+          <t>0.11%1,741,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3988000</v>
+        <v>1741000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,38 +2484,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3376新日興</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.92%183</t>
+          <t>+0.52%19.45</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>183</v>
+        <v>19.45</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.11%1,741,000</t>
+          <t>0.04%5,163,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1741000</v>
+        <v>5163000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,34 +2606,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.52%19.45</t>
+          <t>+7.71%102</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+7.71%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.45</v>
+        <v>102</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0.01%200,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>5163000</v>
+        <v>200000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+7.71%102</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+7.71%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>102</v>
+        <v>436</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.01%200,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+5.44%436</t>
+          <t>-1.33%3700</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>436</v>
+        <v>3700</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.33%3700</t>
+          <t>+0.61%82.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3700</v>
+        <v>82.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.61%82.5</t>
+          <t>+1.06%1435</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>82.5</v>
+        <v>1435</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.06%1435</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1435</v>
+        <v>5610</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.72%5610</t>
+          <t>-1.68%321.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5610</v>
+        <v>321.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,21 +3033,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.68%321.5</t>
+          <t>+2.13%528</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>321.5</v>
+        <v>528</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,21 +3094,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.13%528</t>
+          <t>+0.31%6400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>528</v>
+        <v>6400</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:31</t>
+          <t>2026-08-21 17:26:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3155,21 +3155,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.31%6400</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6400</v>
+        <v>2100</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:32</t>
+          <t>2026-08-21 17:26:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:40</t>
+          <t>2026-08-21 20:03:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:43</t>
+          <t>2026-08-21 20:03:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:45</t>
+          <t>2026-08-21 20:04:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 17:26:46</t>
+          <t>2026-08-21 20:04:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
